--- a/data/ACC-CTB-MOV.xlsx
+++ b/data/ACC-CTB-MOV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rdrodrig\dev\BRA-EUR_international-BRA-EUR-2025\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1546B33E-BA13-439A-B210-C92CDC4552F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF29947-5E9D-46EF-B149-647EFCF819A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4095" yWindow="375" windowWidth="21600" windowHeight="11505" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ACC MOV" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="34">
   <si>
     <t>Month</t>
   </si>
@@ -105,18 +105,9 @@
     <t>ATCO hours productivity</t>
   </si>
   <si>
-    <t>Average transit time in minutes</t>
-  </si>
-  <si>
     <t>IFR ACC Movements</t>
   </si>
   <si>
-    <t>Size of the controlled area</t>
-  </si>
-  <si>
-    <t>Size of OPS room area (m2)</t>
-  </si>
-  <si>
     <t>Number of sectors open at maximum configuration</t>
   </si>
   <si>
@@ -133,6 +124,18 @@
   </si>
   <si>
     <t>CTB</t>
+  </si>
+  <si>
+    <t>Size of the controlled area (million km²)</t>
+  </si>
+  <si>
+    <t>Average transit time (min)</t>
+  </si>
+  <si>
+    <t>Size of OPS room area (m²)</t>
+  </si>
+  <si>
+    <t>LISB</t>
   </si>
 </sst>
 </file>
@@ -211,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -221,23 +224,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,12 +546,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:P15"/>
+  <dimension ref="B2:Q28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>0</v>
@@ -592,356 +596,581 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1">
         <v>2022</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="6">
         <v>28957</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="6">
         <v>25139</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="6">
         <v>29232</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="6">
         <v>30163</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="6">
         <v>32516</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="6">
         <v>28976</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="6">
         <v>33822</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="6">
         <v>32738</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="6">
         <v>31960</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="6">
         <v>32410</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="6">
         <v>32994</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="6">
         <v>34476</v>
       </c>
-      <c r="P3" s="11">
+      <c r="P3" s="7">
         <v>373383</v>
       </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q3" s="12"/>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1">
         <v>2023</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="6">
         <v>33991</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="6">
         <v>28621</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="6">
         <v>33710</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="6">
         <v>32570</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="6">
         <v>34227</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="6">
         <v>32695</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="6">
         <v>35170</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="6">
         <v>35407</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="6">
         <v>32674</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="6">
         <v>31274</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="6">
         <v>31485</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="6">
         <v>32610</v>
       </c>
-      <c r="P4" s="11">
+      <c r="P4" s="7">
         <v>394434</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1">
         <v>2024</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="6">
         <v>30828</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="6">
         <v>31284</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="6">
         <v>43542</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="6">
         <v>43157</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="6">
         <v>41800</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="6">
         <v>39877</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="6">
         <v>44341</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="6">
         <v>44643</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="6">
         <v>41526</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="6">
         <v>42503</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="6">
         <v>43733</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="6">
         <v>45636</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="7">
         <v>492870</v>
       </c>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1">
         <v>2025</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="11"/>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="7"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1">
         <v>2026</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="11"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="7"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1">
         <v>2027</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="11"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="7"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1">
         <v>2028</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="11"/>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="7"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1">
         <v>2029</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="11"/>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="7"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1">
         <v>2030</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="11"/>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="7"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1">
         <v>2031</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="11"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="7"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1">
         <v>2032</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="11"/>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="7"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1">
         <v>2033</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="11"/>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="7"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1">
         <v>2034</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="11"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="7"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D16" s="6">
+        <v>35872</v>
+      </c>
+      <c r="E16" s="6">
+        <v>35098</v>
+      </c>
+      <c r="F16" s="6">
+        <v>43535</v>
+      </c>
+      <c r="G16" s="6">
+        <v>49122</v>
+      </c>
+      <c r="H16" s="6">
+        <v>48336</v>
+      </c>
+      <c r="I16" s="6">
+        <v>49138</v>
+      </c>
+      <c r="J16" s="6">
+        <v>52426</v>
+      </c>
+      <c r="K16" s="6">
+        <v>53141</v>
+      </c>
+      <c r="L16" s="6">
+        <v>50338</v>
+      </c>
+      <c r="M16" s="6">
+        <v>50660</v>
+      </c>
+      <c r="N16" s="6">
+        <v>45189</v>
+      </c>
+      <c r="O16" s="6">
+        <v>48327</v>
+      </c>
+      <c r="P16" s="7">
+        <f>SUM(C16:O16)</f>
+        <v>563204</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D17" s="6">
+        <v>46578</v>
+      </c>
+      <c r="E17" s="6">
+        <v>44469</v>
+      </c>
+      <c r="F17" s="6">
+        <v>49873</v>
+      </c>
+      <c r="G17" s="6">
+        <v>51734</v>
+      </c>
+      <c r="H17" s="6">
+        <v>51064</v>
+      </c>
+      <c r="I17" s="6">
+        <v>52315</v>
+      </c>
+      <c r="J17" s="6">
+        <v>56252</v>
+      </c>
+      <c r="K17" s="6">
+        <v>56690</v>
+      </c>
+      <c r="L17" s="6">
+        <v>54224</v>
+      </c>
+      <c r="M17" s="6">
+        <v>56079</v>
+      </c>
+      <c r="N17" s="6">
+        <v>49491</v>
+      </c>
+      <c r="O17" s="6">
+        <v>52527</v>
+      </c>
+      <c r="P17" s="7">
+        <f t="shared" ref="P17:P18" si="0">SUM(C17:O17)</f>
+        <v>623319</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2024</v>
+      </c>
+      <c r="D18" s="6">
+        <v>49325</v>
+      </c>
+      <c r="E18" s="6">
+        <v>48495</v>
+      </c>
+      <c r="F18" s="6">
+        <v>55549</v>
+      </c>
+      <c r="G18" s="6">
+        <v>55746</v>
+      </c>
+      <c r="H18" s="6">
+        <v>56322</v>
+      </c>
+      <c r="I18" s="6">
+        <v>56498</v>
+      </c>
+      <c r="J18" s="6">
+        <v>60650</v>
+      </c>
+      <c r="K18" s="6">
+        <v>60763</v>
+      </c>
+      <c r="L18" s="6">
+        <v>57808</v>
+      </c>
+      <c r="M18" s="6">
+        <v>59171</v>
+      </c>
+      <c r="N18" s="6">
+        <v>53257</v>
+      </c>
+      <c r="O18" s="6">
+        <v>55491</v>
+      </c>
+      <c r="P18" s="7">
+        <f t="shared" si="0"/>
+        <v>671099</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2034</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -961,7 +1190,7 @@
     <col min="6" max="6" width="11.7109375" style="4" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" style="4" customWidth="1"/>
     <col min="10" max="10" width="12.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -969,117 +1198,117 @@
     <col min="14" max="16384" width="15.5703125" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="2:13" s="11" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="I2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="M2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="9" t="s">
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="9">
+        <v>462470</v>
+      </c>
+      <c r="E3" s="9">
+        <v>188038</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0.53690000000000004</v>
+      </c>
+      <c r="G3" s="8">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="H3" s="9">
+        <v>492870</v>
+      </c>
+      <c r="I3" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="J3" s="8">
+        <v>208</v>
+      </c>
+      <c r="K3" s="8">
+        <v>405</v>
+      </c>
+      <c r="L3" s="8">
+        <v>13</v>
+      </c>
+      <c r="M3" s="9">
+        <v>45606</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="9">
+        <v>345602</v>
+      </c>
+      <c r="E4" s="9">
+        <v>153644</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="6">
-        <v>462470</v>
-      </c>
-      <c r="E3" s="6">
-        <v>188038</v>
-      </c>
-      <c r="F3" s="7">
-        <v>0.53690000000000004</v>
-      </c>
-      <c r="G3" s="5">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="H3" s="6">
-        <v>492870</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1.7</v>
-      </c>
-      <c r="J3" s="5">
-        <v>208</v>
-      </c>
-      <c r="K3" s="5">
-        <v>405</v>
-      </c>
-      <c r="L3" s="5">
-        <v>13</v>
-      </c>
-      <c r="M3" s="6">
-        <v>45606</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="6">
-        <v>345602</v>
-      </c>
-      <c r="E4" s="6">
-        <v>153644</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="G4" s="8">
         <v>37</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="9">
         <v>560992</v>
       </c>
-      <c r="I4" s="5">
-        <v>671000</v>
-      </c>
-      <c r="J4" s="5">
+      <c r="I4" s="8">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="J4" s="8">
         <v>71</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="8">
         <v>663</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="8">
         <v>9</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="9">
         <v>47147</v>
       </c>
     </row>
